--- a/resources/templates/bvid.xlsx
+++ b/resources/templates/bvid.xlsx
@@ -1,199 +1,299 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+  <si>
+    <t>数据获取时间：2026-05-16 18:20:21</t>
+  </si>
+  <si>
+    <t>播放得点</t>
+  </si>
+  <si>
+    <t>自动覆写</t>
+  </si>
+  <si>
+    <t>播放量</t>
+  </si>
+  <si>
+    <t>点赞量</t>
+  </si>
+  <si>
+    <t>弹幕量</t>
+  </si>
+  <si>
+    <t>评论量</t>
+  </si>
+  <si>
+    <t>硬币量</t>
+  </si>
+  <si>
+    <t>收藏量</t>
+  </si>
+  <si>
+    <t>互动得点</t>
+  </si>
+  <si>
+    <t>本期数据</t>
+  </si>
+  <si>
+    <t>收藏得点</t>
+  </si>
+  <si>
+    <t>总数据</t>
+  </si>
+  <si>
+    <t>硬币得点</t>
+  </si>
+  <si>
+    <t>历史数据</t>
+  </si>
+  <si>
+    <t>点赞得点</t>
+  </si>
+  <si>
+    <t>公式来源:中V周刊组</t>
+  </si>
+  <si>
+    <t>计算器制作人:云师阳(1866643210)</t>
+  </si>
+  <si>
+    <t>最终得点</t>
+  </si>
+  <si>
+    <t>计算过程</t>
+  </si>
+  <si>
+    <t>基础播点</t>
+  </si>
+  <si>
+    <t>互动量</t>
+  </si>
+  <si>
+    <t>修正A</t>
+  </si>
+  <si>
+    <t>修正B</t>
+  </si>
+  <si>
+    <t>修正C</t>
+  </si>
+  <si>
+    <t>修正D</t>
+  </si>
+  <si>
+    <t>请在手动填写区写下往期数据。行数超出表格已给出量的话请修改第5行求和逻辑。若计算器未减去历史数据，请重新输入以刷新缓存</t>
+  </si>
+  <si>
+    <t>手动填写</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="23">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -385,7 +485,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -603,208 +703,197 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="15" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="14" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -858,203 +947,140 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>298000</colOff>
-      <row>18</row>
-      <rowOff>90600</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="图片 1"/>
-        <cNvPicPr>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>298000</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>90600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="6019800" y="0"/>
           <a:ext cx="3726815" cy="3290570"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>16</col>
-      <colOff>279400</colOff>
-      <row>0</row>
-      <rowOff>69850</rowOff>
-    </from>
-    <to>
-      <col>21</col>
-      <colOff>577400</colOff>
-      <row>17</row>
-      <rowOff>134250</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="图片 2"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>577400</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>134250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="9728200" y="69850"/>
           <a:ext cx="3726815" cy="3086735"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>21</col>
-      <colOff>596000</colOff>
-      <row>29</row>
-      <rowOff>148000</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="图片 3"/>
-        <cNvPicPr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>596000</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>148000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="6019800" y="3378200"/>
           <a:ext cx="7453630" cy="1925955"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <avLst/>
+          <a:avLst/>
         </a:prstGeom>
         <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1313,416 +1339,334 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="9.16666666666667" customWidth="1" style="1" min="1" max="1"/>
-    <col width="8.58333333333333" customWidth="1" min="2" max="2"/>
-    <col width="6.58333333333333" customWidth="1" min="3" max="7"/>
-    <col width="4.58333333333333" customWidth="1" min="8" max="8"/>
-    <col width="8.58333333333333" customWidth="1" style="1" min="9" max="9"/>
-    <col width="10.5833333333333" customWidth="1" style="2" min="10" max="10"/>
-    <col width="4.58333333333333" customWidth="1" min="11" max="11"/>
+    <col min="1" max="1" width="9.16666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.58333333333333" customWidth="1"/>
+    <col min="3" max="7" width="6.58333333333333" customWidth="1"/>
+    <col min="8" max="8" width="4.58333333333333" customWidth="1"/>
+    <col min="9" max="9" width="8.58333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5833333333333" style="2" customWidth="1"/>
+    <col min="11" max="11" width="4.58333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>数据获取时间：2026-05-16 17:16:00</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="5" t="n"/>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>播放得点</t>
-        </is>
+    <row r="1" spans="1:10">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
+      <c r="I1" s="7" t="s">
+        <v>1</v>
       </c>
       <c r="J1" s="15">
         <f>B9*G9</f>
-        <v/>
+        <v>2468.75362559045</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>自动覆写</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>播放量</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>点赞量</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>弹幕量</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>评论量</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>硬币量</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>收藏量</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>互动得点</t>
-        </is>
+    <row r="2" spans="1:10">
+      <c r="A2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="J2" s="15">
         <f>C9*D9*15</f>
-        <v/>
+        <v>1622.6313647902</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>本期数据</t>
-        </is>
+    <row r="3" spans="1:10">
+      <c r="A3" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="B3" s="9">
-        <f>B4-B5</f>
-        <v/>
+        <f t="shared" ref="B3:G3" si="0">B4-B5</f>
+        <v>12067</v>
       </c>
       <c r="C3" s="9">
-        <f>C4-C5</f>
-        <v/>
+        <f t="shared" si="0"/>
+        <v>2201</v>
       </c>
       <c r="D3" s="9">
-        <f>D4-D5</f>
-        <v/>
+        <f t="shared" si="0"/>
+        <v>105</v>
       </c>
       <c r="E3" s="9">
-        <f>E4-E5</f>
-        <v/>
+        <f t="shared" si="0"/>
+        <v>87</v>
       </c>
       <c r="F3" s="9">
-        <f>F4-F5</f>
-        <v/>
+        <f t="shared" si="0"/>
+        <v>108</v>
       </c>
       <c r="G3" s="9">
-        <f>G4-G5</f>
-        <v/>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>收藏得点</t>
-        </is>
+        <f t="shared" si="0"/>
+        <v>524</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>11</v>
       </c>
       <c r="J3" s="15">
         <f>G3*E9</f>
-        <v/>
+        <v>966.603132510152</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>总数据</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>12026</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>2196</v>
-      </c>
-      <c r="D4" s="9" t="n">
+    <row r="4" spans="1:10">
+      <c r="A4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="9">
+        <v>12067</v>
+      </c>
+      <c r="C4" s="9">
+        <v>2201</v>
+      </c>
+      <c r="D4" s="9">
         <v>105</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="9">
         <v>87</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="9">
         <v>108</v>
       </c>
-      <c r="G4" s="9" t="n">
-        <v>522</v>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>硬币得点</t>
-        </is>
+      <c r="G4" s="9">
+        <v>524</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="J4" s="15">
         <f>F3*F9</f>
-        <v/>
+        <v>241.650783127538</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>历史数据</t>
-        </is>
+    <row r="5" spans="1:10">
+      <c r="A5" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="B5" s="10">
-        <f>SUM(B12:B15)</f>
-        <v/>
+        <f t="shared" ref="B5:G5" si="1">SUM(B12:B15)</f>
+        <v>0</v>
       </c>
       <c r="C5" s="10">
-        <f>SUM(C12:C15)</f>
-        <v/>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="D5" s="10">
-        <f>SUM(D12:D15)</f>
-        <v/>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="E5" s="10">
-        <f>SUM(E12:E15)</f>
-        <v/>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="F5" s="10">
-        <f>SUM(F12:F15)</f>
-        <v/>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="G5" s="10">
-        <f>SUM(G12:G15)</f>
-        <v/>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>点赞得点</t>
-        </is>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="J5" s="15">
         <f>IF(C3&gt;F3*2,F3*2,C3)</f>
-        <v/>
+        <v>216</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>公式来源:中V周刊组</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>计算器制作人:云师阳(1866643210)</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>最终得点</t>
-        </is>
+    <row r="6" spans="1:10">
+      <c r="A6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="I6" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J6" s="15">
         <f>SUM(J1:J5)</f>
-        <v/>
+        <v>5515.63890601834</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>计算过程</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>基础播点</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>互动量</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>修正A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>修正B</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>修正C</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>修正D</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>请在手动填写区写下往期数据。行数超出表格已给出量的话请修改第5行求和逻辑。若计算器未减去历史数据，请重新输入以刷新缓存</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="n"/>
+    <row r="8" spans="1:10">
+      <c r="A8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="17"/>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="n"/>
+    <row r="9" spans="1:10">
+      <c r="A9" s="14"/>
       <c r="B9" s="9">
         <f>IF(B3&gt;10000,B3*0.5+5000,B3)</f>
-        <v/>
+        <v>11033.5</v>
       </c>
       <c r="C9" s="9">
         <f>E3+D3</f>
-        <v/>
+        <v>192</v>
       </c>
       <c r="D9" s="15">
         <f>((B9+G3)/(B9+G3+C9*20))^2</f>
-        <v/>
+        <v>0.563413668329929</v>
       </c>
       <c r="E9" s="15">
         <f>IF(IF(G3&gt;F3*2,(F3^2/(B3*G3))*1000,(G3/B3)*250)&gt;50,50,IF(G3&gt;F3*2,(F3^2/(B3*G3))*1000,(G3/B3)*250))</f>
-        <v/>
+        <v>1.84466246662243</v>
       </c>
       <c r="F9" s="15">
         <f>IF(IF(F3&gt;G3,(G3^2/(B3*F3))*250,(F3/B3)*250)&gt;50,50,IF(F3&gt;G3,(G3^2/(B3*F3))*250,(F3/B3)*250))</f>
-        <v/>
+        <v>2.23750725118091</v>
       </c>
       <c r="G9" s="15">
         <f>IF(IF(G3&gt;F3,(F3/B3)*25,(G3/B3)*25)&gt;1,1,IF(G3&gt;F3,(F3/B3)*25,(G3/B3)*25))</f>
-        <v/>
-      </c>
-      <c r="I9" s="18" t="n"/>
-      <c r="J9" s="19" t="n"/>
+        <v>0.223750725118091</v>
+      </c>
+      <c r="I9" s="18"/>
+      <c r="J9" s="19"/>
     </row>
-    <row r="10">
-      <c r="I10" s="18" t="n"/>
-      <c r="J10" s="19" t="n"/>
+    <row r="10" spans="9:10">
+      <c r="I10" s="18"/>
+      <c r="J10" s="19"/>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>手动填写</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>播放量</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>点赞量</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>弹幕量</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>评论量</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>硬币量</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>收藏量</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="n"/>
-      <c r="J11" s="19" t="n"/>
+    <row r="11" spans="1:10">
+      <c r="A11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="18"/>
+      <c r="J11" s="19"/>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
+    <row r="12" spans="1:10">
+      <c r="A12" s="8">
         <v>20260516</v>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="18" t="n"/>
-      <c r="J12" s="19" t="n"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="19"/>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
+    <row r="13" spans="1:10">
+      <c r="A13" s="8">
         <v>20260523</v>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="21" t="n"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="21"/>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
+    <row r="14" spans="1:7">
+      <c r="A14" s="8">
         <v>20260530</v>
       </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
+    <row r="15" spans="1:7">
+      <c r="A15" s="8">
         <v>20260606</v>
       </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C6:G6"/>
     <mergeCell ref="I8:J13"/>
-    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>